--- a/rtss-pre1917/src/main/resources/excel-templates/composite-taxon-1881-1913.xlsx
+++ b/rtss-pre1917/src/main/resources/excel-templates/composite-taxon-1881-1913.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\excel-templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4AE2F32-F1E3-4215-B49B-26CBD5D6CD0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29449993-9F6E-4A14-A66E-63416D7FE280}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{BB18BFB1-C03A-41FE-BE1A-93D139757D6D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="23520" xr2:uid="{BB18BFB1-C03A-41FE-BE1A-93D139757D6D}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="16">
   <si>
     <t>XXX</t>
   </si>
@@ -106,6 +106,9 @@
   </si>
   <si>
     <t>1881-1913</t>
+  </si>
+  <si>
+    <t>%учёта</t>
   </si>
 </sst>
 </file>
@@ -195,7 +198,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -215,7 +218,6 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3009,13 +3011,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>12</xdr:col>
+      <xdr:col>13</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>284797</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>33</xdr:col>
+      <xdr:col>34</xdr:col>
       <xdr:colOff>619125</xdr:colOff>
       <xdr:row>47</xdr:row>
       <xdr:rowOff>9525</xdr:rowOff>
@@ -3045,13 +3047,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>12</xdr:col>
+      <xdr:col>13</xdr:col>
       <xdr:colOff>952</xdr:colOff>
       <xdr:row>47</xdr:row>
       <xdr:rowOff>170497</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>33</xdr:col>
+      <xdr:col>34</xdr:col>
       <xdr:colOff>617220</xdr:colOff>
       <xdr:row>97</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
@@ -3399,19 +3401,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12B321D7-C433-4B50-AA6E-BF1C75F28F7F}">
-  <dimension ref="A1:K42"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <dimension ref="A1:L42"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.26171875" customWidth="1"/>
-    <col min="2" max="2" width="14.578125" customWidth="1"/>
-    <col min="3" max="3" width="16.3125" customWidth="1"/>
-    <col min="4" max="4" width="13.15625" customWidth="1"/>
-    <col min="5" max="5" width="15.578125" customWidth="1"/>
-    <col min="6" max="7" width="9.26171875" bestFit="1" customWidth="1"/>
-    <col min="8" max="11" width="8.89453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.28515625" customWidth="1"/>
+    <col min="2" max="2" width="14.5703125" customWidth="1"/>
+    <col min="3" max="3" width="16.28515625" customWidth="1"/>
+    <col min="4" max="4" width="13.140625" customWidth="1"/>
+    <col min="5" max="5" width="15.5703125" customWidth="1"/>
+    <col min="6" max="7" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="11" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="23.1" x14ac:dyDescent="0.85">
+    <row r="1" spans="1:12" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -3425,7 +3428,7 @@
       <c r="I1" s="6"/>
       <c r="J1" s="6"/>
     </row>
-    <row r="2" spans="1:11" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="2" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3437,31 +3440,32 @@
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
     </row>
-    <row r="3" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="16" t="s">
+      <c r="B3" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="16"/>
-      <c r="D3" s="17" t="s">
+      <c r="C3" s="15"/>
+      <c r="D3" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
-      <c r="G3" s="17"/>
-      <c r="H3" s="17"/>
-      <c r="I3" s="17"/>
-      <c r="J3" s="17"/>
-      <c r="K3" s="9"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="16"/>
+      <c r="I3" s="16"/>
+      <c r="J3" s="16"/>
+      <c r="K3" s="16"/>
+      <c r="L3" s="16"/>
     </row>
-    <row r="4" spans="1:11" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="8"/>
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="15" t="s">
+      <c r="C4" s="14" t="s">
         <v>3</v>
       </c>
       <c r="D4" s="8" t="s">
@@ -3488,8 +3492,11 @@
       <c r="K4" s="8" t="s">
         <v>10</v>
       </c>
+      <c r="L4" s="8" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="5" spans="1:11" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="5" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>1881</v>
       </c>
@@ -3497,7 +3504,7 @@
         <f>D5 + 100000</f>
         <v>1100000</v>
       </c>
-      <c r="C5" s="10">
+      <c r="C5" s="9">
         <f>(B5+B6) /2</f>
         <v>1110025</v>
       </c>
@@ -3525,22 +3532,26 @@
         <f>G5/E5*1000</f>
         <v>29.702235093190762</v>
       </c>
-      <c r="K5" s="11">
+      <c r="K5" s="10">
         <f>I5-J5</f>
         <v>19.801490062127176</v>
       </c>
+      <c r="L5" s="10">
+        <f>E5/C5*100</f>
+        <v>90.991193892029457</v>
+      </c>
     </row>
-    <row r="6" spans="1:11" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="6" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <f>A5+1</f>
         <v>1882</v>
       </c>
       <c r="B6" s="4">
-        <f t="shared" ref="B6:B39" si="0">D6 + 100000</f>
+        <f t="shared" ref="B6:B38" si="0">D6 + 100000</f>
         <v>1120050</v>
       </c>
-      <c r="C6" s="10">
-        <f t="shared" ref="C6:C38" si="1">(B6+B7) /2</f>
+      <c r="C6" s="9">
+        <f t="shared" ref="C6:C37" si="1">(B6+B7) /2</f>
         <v>1130080</v>
       </c>
       <c r="D6" s="4">
@@ -3548,7 +3559,7 @@
         <v>1020050</v>
       </c>
       <c r="E6" s="4">
-        <f t="shared" ref="E6:E38" si="2">(D6+D7) /2</f>
+        <f t="shared" ref="E6:E37" si="2">(D6+D7) /2</f>
         <v>1030080</v>
       </c>
       <c r="F6" s="4">
@@ -3564,33 +3575,37 @@
         <v>60</v>
       </c>
       <c r="I6" s="5">
-        <f t="shared" ref="I6:I38" si="3">F6/E6*1000</f>
+        <f t="shared" ref="I6:I37" si="3">F6/E6*1000</f>
         <v>48.636999068033553</v>
       </c>
       <c r="J6" s="5">
-        <f t="shared" ref="J6:J38" si="4">G6/E6*1000</f>
+        <f t="shared" ref="J6:J37" si="4">G6/E6*1000</f>
         <v>29.22103137620379</v>
       </c>
-      <c r="K6" s="11">
-        <f t="shared" ref="K6:K38" si="5">I6-J6</f>
+      <c r="K6" s="10">
+        <f t="shared" ref="K6:K37" si="5">I6-J6</f>
         <v>19.415967691829763</v>
       </c>
+      <c r="L6" s="10">
+        <f t="shared" ref="L6:L37" si="6">E6/C6*100</f>
+        <v>91.151068950870737</v>
+      </c>
     </row>
-    <row r="7" spans="1:11" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="7" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
-        <f t="shared" ref="A7:A37" si="6">A6+1</f>
+        <f t="shared" ref="A7:A37" si="7">A6+1</f>
         <v>1883</v>
       </c>
       <c r="B7" s="4">
         <f t="shared" si="0"/>
         <v>1140110</v>
       </c>
-      <c r="C7" s="10">
+      <c r="C7" s="9">
         <f t="shared" si="1"/>
         <v>1150145</v>
       </c>
       <c r="D7" s="4">
-        <f t="shared" ref="D7:D39" si="7">D6+F6-G6+H6</f>
+        <f t="shared" ref="D7:D38" si="8">D6+F6-G6+H6</f>
         <v>1040110</v>
       </c>
       <c r="E7" s="4">
@@ -3598,15 +3613,15 @@
         <v>1050145</v>
       </c>
       <c r="F7" s="4">
-        <f t="shared" ref="F7:F38" si="8">F6+100</f>
+        <f t="shared" ref="F7:F37" si="9">F6+100</f>
         <v>50200</v>
       </c>
       <c r="G7" s="4">
-        <f t="shared" ref="G7:G38" si="9">G6+100</f>
+        <f t="shared" ref="G7:G37" si="10">G6+100</f>
         <v>30200</v>
       </c>
       <c r="H7" s="4">
-        <f t="shared" ref="H7:H38" si="10">H6+10</f>
+        <f t="shared" ref="H7:H37" si="11">H6+10</f>
         <v>70</v>
       </c>
       <c r="I7" s="5">
@@ -3617,26 +3632,30 @@
         <f t="shared" si="4"/>
         <v>28.757933428240861</v>
       </c>
-      <c r="K7" s="11">
+      <c r="K7" s="10">
         <f t="shared" si="5"/>
         <v>19.04498902532508</v>
       </c>
+      <c r="L7" s="10">
+        <f t="shared" si="6"/>
+        <v>91.305444096179173</v>
+      </c>
     </row>
-    <row r="8" spans="1:11" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="8" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1884</v>
       </c>
       <c r="B8" s="4">
         <f t="shared" si="0"/>
         <v>1160180</v>
       </c>
-      <c r="C8" s="10">
+      <c r="C8" s="9">
         <f t="shared" si="1"/>
         <v>1170220</v>
       </c>
       <c r="D8" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1060180</v>
       </c>
       <c r="E8" s="4">
@@ -3644,15 +3663,15 @@
         <v>1070220</v>
       </c>
       <c r="F8" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>50300</v>
       </c>
       <c r="G8" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>30300</v>
       </c>
       <c r="H8" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>80</v>
       </c>
       <c r="I8" s="5">
@@ -3663,26 +3682,30 @@
         <f t="shared" si="4"/>
         <v>28.311935863654202</v>
       </c>
-      <c r="K8" s="11">
+      <c r="K8" s="10">
         <f t="shared" si="5"/>
         <v>18.687746444656238</v>
       </c>
+      <c r="L8" s="10">
+        <f t="shared" si="6"/>
+        <v>91.454598280665181</v>
+      </c>
     </row>
-    <row r="9" spans="1:11" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="9" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1885</v>
       </c>
       <c r="B9" s="4">
         <f t="shared" si="0"/>
         <v>1180260</v>
       </c>
-      <c r="C9" s="10">
+      <c r="C9" s="9">
         <f t="shared" si="1"/>
         <v>1190305</v>
       </c>
       <c r="D9" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1080260</v>
       </c>
       <c r="E9" s="4">
@@ -3690,15 +3713,15 @@
         <v>1090305</v>
       </c>
       <c r="F9" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>50400</v>
       </c>
       <c r="G9" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>30400</v>
       </c>
       <c r="H9" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>90</v>
       </c>
       <c r="I9" s="5">
@@ -3709,26 +3732,30 @@
         <f t="shared" si="4"/>
         <v>27.882106383076298</v>
       </c>
-      <c r="K9" s="11">
+      <c r="K9" s="10">
         <f t="shared" si="5"/>
         <v>18.343491041497558</v>
       </c>
+      <c r="L9" s="10">
+        <f t="shared" si="6"/>
+        <v>91.598791906276119</v>
+      </c>
     </row>
-    <row r="10" spans="1:11" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="10" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1886</v>
       </c>
       <c r="B10" s="4">
         <f t="shared" si="0"/>
         <v>1200350</v>
       </c>
-      <c r="C10" s="10">
+      <c r="C10" s="9">
         <f t="shared" si="1"/>
         <v>1210400</v>
       </c>
       <c r="D10" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1100350</v>
       </c>
       <c r="E10" s="4">
@@ -3736,15 +3763,15 @@
         <v>1110400</v>
       </c>
       <c r="F10" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>50500</v>
       </c>
       <c r="G10" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>30500</v>
       </c>
       <c r="H10" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>100</v>
       </c>
       <c r="I10" s="5">
@@ -3755,26 +3782,30 @@
         <f t="shared" si="4"/>
         <v>27.467579250720462</v>
       </c>
-      <c r="K10" s="11">
+      <c r="K10" s="10">
         <f t="shared" si="5"/>
         <v>18.01152737752161</v>
       </c>
+      <c r="L10" s="10">
+        <f t="shared" si="6"/>
+        <v>91.738268341044289</v>
+      </c>
     </row>
-    <row r="11" spans="1:11" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="11" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1887</v>
       </c>
       <c r="B11" s="4">
         <f t="shared" si="0"/>
         <v>1220450</v>
       </c>
-      <c r="C11" s="10">
+      <c r="C11" s="9">
         <f t="shared" si="1"/>
         <v>1230505</v>
       </c>
       <c r="D11" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1120450</v>
       </c>
       <c r="E11" s="4">
@@ -3782,15 +3813,15 @@
         <v>1130505</v>
       </c>
       <c r="F11" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>50600</v>
       </c>
       <c r="G11" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>30600</v>
       </c>
       <c r="H11" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>110</v>
       </c>
       <c r="I11" s="5">
@@ -3801,26 +3832,30 @@
         <f t="shared" si="4"/>
         <v>27.067549457985589</v>
       </c>
-      <c r="K11" s="11">
+      <c r="K11" s="10">
         <f t="shared" si="5"/>
         <v>17.691208796069017</v>
       </c>
+      <c r="L11" s="10">
+        <f t="shared" si="6"/>
+        <v>91.873255289494963</v>
+      </c>
     </row>
-    <row r="12" spans="1:11" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="12" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1888</v>
       </c>
       <c r="B12" s="4">
         <f t="shared" si="0"/>
         <v>1240560</v>
       </c>
-      <c r="C12" s="10">
+      <c r="C12" s="9">
         <f t="shared" si="1"/>
         <v>1250620</v>
       </c>
       <c r="D12" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1140560</v>
       </c>
       <c r="E12" s="4">
@@ -3828,15 +3863,15 @@
         <v>1150620</v>
       </c>
       <c r="F12" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>50700</v>
       </c>
       <c r="G12" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>30700</v>
       </c>
       <c r="H12" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>120</v>
       </c>
       <c r="I12" s="5">
@@ -3847,26 +3882,30 @@
         <f t="shared" si="4"/>
         <v>26.681267490570303</v>
       </c>
-      <c r="K12" s="11">
+      <c r="K12" s="10">
         <f t="shared" si="5"/>
         <v>17.38193321861257</v>
       </c>
+      <c r="L12" s="10">
+        <f t="shared" si="6"/>
+        <v>92.0039660328477</v>
+      </c>
     </row>
-    <row r="13" spans="1:11" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="13" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1889</v>
       </c>
       <c r="B13" s="4">
         <f t="shared" si="0"/>
         <v>1260680</v>
       </c>
-      <c r="C13" s="10">
+      <c r="C13" s="9">
         <f t="shared" si="1"/>
         <v>1270745</v>
       </c>
       <c r="D13" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1160680</v>
       </c>
       <c r="E13" s="4">
@@ -3874,15 +3913,15 @@
         <v>1170745</v>
       </c>
       <c r="F13" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>50800</v>
       </c>
       <c r="G13" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>30800</v>
       </c>
       <c r="H13" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>130</v>
       </c>
       <c r="I13" s="5">
@@ -3893,26 +3932,30 @@
         <f t="shared" si="4"/>
         <v>26.308034627523501</v>
       </c>
-      <c r="K13" s="11">
+      <c r="K13" s="10">
         <f t="shared" si="5"/>
         <v>17.083139368521753</v>
       </c>
+      <c r="L13" s="10">
+        <f t="shared" si="6"/>
+        <v>92.130600553218784</v>
+      </c>
     </row>
-    <row r="14" spans="1:11" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="14" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1890</v>
       </c>
       <c r="B14" s="4">
         <f t="shared" si="0"/>
         <v>1280810</v>
       </c>
-      <c r="C14" s="10">
+      <c r="C14" s="9">
         <f t="shared" si="1"/>
         <v>1290880</v>
       </c>
       <c r="D14" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1180810</v>
       </c>
       <c r="E14" s="4">
@@ -3920,15 +3963,15 @@
         <v>1190880</v>
       </c>
       <c r="F14" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>50900</v>
       </c>
       <c r="G14" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>30900</v>
       </c>
       <c r="H14" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>140</v>
       </c>
       <c r="I14" s="5">
@@ -3939,26 +3982,30 @@
         <f t="shared" si="4"/>
         <v>25.947198710197501</v>
       </c>
-      <c r="K14" s="11">
+      <c r="K14" s="10">
         <f t="shared" si="5"/>
         <v>16.794303372296117</v>
       </c>
+      <c r="L14" s="10">
+        <f t="shared" si="6"/>
+        <v>92.253346554288555</v>
+      </c>
     </row>
-    <row r="15" spans="1:11" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="15" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1891</v>
       </c>
       <c r="B15" s="4">
         <f t="shared" si="0"/>
         <v>1300950</v>
       </c>
-      <c r="C15" s="10">
+      <c r="C15" s="9">
         <f t="shared" si="1"/>
         <v>1311025</v>
       </c>
       <c r="D15" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1200950</v>
       </c>
       <c r="E15" s="4">
@@ -3966,15 +4013,15 @@
         <v>1211025</v>
       </c>
       <c r="F15" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>51000</v>
       </c>
       <c r="G15" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>31000</v>
       </c>
       <c r="H15" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>150</v>
       </c>
       <c r="I15" s="5">
@@ -3985,26 +4032,30 @@
         <f t="shared" si="4"/>
         <v>25.598150327202166</v>
       </c>
-      <c r="K15" s="11">
+      <c r="K15" s="10">
         <f t="shared" si="5"/>
         <v>16.514935694969136</v>
       </c>
+      <c r="L15" s="10">
+        <f t="shared" si="6"/>
+        <v>92.372380389389988</v>
+      </c>
     </row>
-    <row r="16" spans="1:11" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="16" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1892</v>
       </c>
       <c r="B16" s="4">
         <f t="shared" si="0"/>
         <v>1321100</v>
       </c>
-      <c r="C16" s="10">
+      <c r="C16" s="9">
         <f t="shared" si="1"/>
         <v>1331180</v>
       </c>
       <c r="D16" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1221100</v>
       </c>
       <c r="E16" s="4">
@@ -4012,15 +4063,15 @@
         <v>1231180</v>
       </c>
       <c r="F16" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>51100</v>
       </c>
       <c r="G16" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>31100</v>
       </c>
       <c r="H16" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>160</v>
       </c>
       <c r="I16" s="5">
@@ -4031,26 +4082,30 @@
         <f t="shared" si="4"/>
         <v>25.260319368410791</v>
       </c>
-      <c r="K16" s="11">
+      <c r="K16" s="10">
         <f t="shared" si="5"/>
         <v>16.244578371968352</v>
       </c>
+      <c r="L16" s="10">
+        <f t="shared" si="6"/>
+        <v>92.48786790666928</v>
+      </c>
     </row>
-    <row r="17" spans="1:11" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="17" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1893</v>
       </c>
       <c r="B17" s="4">
         <f t="shared" si="0"/>
         <v>1341260</v>
       </c>
-      <c r="C17" s="10">
+      <c r="C17" s="9">
         <f t="shared" si="1"/>
         <v>1351345</v>
       </c>
       <c r="D17" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1241260</v>
       </c>
       <c r="E17" s="4">
@@ -4058,15 +4113,15 @@
         <v>1251345</v>
       </c>
       <c r="F17" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>51200</v>
       </c>
       <c r="G17" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>31200</v>
       </c>
       <c r="H17" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>170</v>
       </c>
       <c r="I17" s="5">
@@ -4077,26 +4132,30 @@
         <f t="shared" si="4"/>
         <v>24.933171907028036</v>
       </c>
-      <c r="K17" s="11">
+      <c r="K17" s="10">
         <f t="shared" si="5"/>
         <v>15.982802504505155</v>
       </c>
+      <c r="L17" s="10">
+        <f t="shared" si="6"/>
+        <v>92.599965219836534</v>
+      </c>
     </row>
-    <row r="18" spans="1:11" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="18" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1894</v>
       </c>
       <c r="B18" s="4">
         <f t="shared" si="0"/>
         <v>1361430</v>
       </c>
-      <c r="C18" s="10">
+      <c r="C18" s="9">
         <f t="shared" si="1"/>
         <v>1371520</v>
       </c>
       <c r="D18" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1261430</v>
       </c>
       <c r="E18" s="4">
@@ -4104,15 +4163,15 @@
         <v>1271520</v>
       </c>
       <c r="F18" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>51300</v>
       </c>
       <c r="G18" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>31300</v>
       </c>
       <c r="H18" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>180</v>
       </c>
       <c r="I18" s="5">
@@ -4123,26 +4182,30 @@
         <f t="shared" si="4"/>
         <v>24.616207373851765</v>
       </c>
-      <c r="K18" s="11">
+      <c r="K18" s="10">
         <f t="shared" si="5"/>
         <v>15.729205989681645</v>
       </c>
+      <c r="L18" s="10">
+        <f t="shared" si="6"/>
+        <v>92.708819412039205</v>
+      </c>
     </row>
-    <row r="19" spans="1:11" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="19" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1895</v>
       </c>
       <c r="B19" s="4">
         <f t="shared" si="0"/>
         <v>1381610</v>
       </c>
-      <c r="C19" s="10">
+      <c r="C19" s="9">
         <f t="shared" si="1"/>
         <v>1391705</v>
       </c>
       <c r="D19" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1281610</v>
       </c>
       <c r="E19" s="4">
@@ -4150,15 +4213,15 @@
         <v>1291705</v>
       </c>
       <c r="F19" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>51400</v>
       </c>
       <c r="G19" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>31400</v>
       </c>
       <c r="H19" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>190</v>
       </c>
       <c r="I19" s="5">
@@ -4169,26 +4232,30 @@
         <f t="shared" si="4"/>
         <v>24.308955992273777</v>
       </c>
-      <c r="K19" s="11">
+      <c r="K19" s="10">
         <f t="shared" si="5"/>
         <v>15.483411460046998</v>
       </c>
+      <c r="L19" s="10">
+        <f t="shared" si="6"/>
+        <v>92.814569179531574</v>
+      </c>
     </row>
-    <row r="20" spans="1:11" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="20" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1896</v>
       </c>
       <c r="B20" s="4">
         <f t="shared" si="0"/>
         <v>1401800</v>
       </c>
-      <c r="C20" s="10">
+      <c r="C20" s="9">
         <f t="shared" si="1"/>
         <v>1411900</v>
       </c>
       <c r="D20" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1301800</v>
       </c>
       <c r="E20" s="4">
@@ -4196,15 +4263,15 @@
         <v>1311900</v>
       </c>
       <c r="F20" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>51500</v>
       </c>
       <c r="G20" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>31500</v>
       </c>
       <c r="H20" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>200</v>
       </c>
       <c r="I20" s="5">
@@ -4215,26 +4282,30 @@
         <f t="shared" si="4"/>
         <v>24.010976446375484</v>
       </c>
-      <c r="K20" s="11">
+      <c r="K20" s="10">
         <f t="shared" si="5"/>
         <v>15.245064410397131</v>
       </c>
+      <c r="L20" s="10">
+        <f t="shared" si="6"/>
+        <v>92.917345421063814</v>
+      </c>
     </row>
-    <row r="21" spans="1:11" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="21" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1897</v>
       </c>
       <c r="B21" s="4">
         <f t="shared" si="0"/>
         <v>1422000</v>
       </c>
-      <c r="C21" s="10">
+      <c r="C21" s="9">
         <f t="shared" si="1"/>
         <v>1432105</v>
       </c>
       <c r="D21" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1322000</v>
       </c>
       <c r="E21" s="4">
@@ -4242,15 +4313,15 @@
         <v>1332105</v>
       </c>
       <c r="F21" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>51600</v>
       </c>
       <c r="G21" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>31600</v>
       </c>
       <c r="H21" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>210</v>
       </c>
       <c r="I21" s="5">
@@ -4261,26 +4332,30 @@
         <f t="shared" si="4"/>
         <v>23.721853757774351</v>
       </c>
-      <c r="K21" s="11">
+      <c r="K21" s="10">
         <f t="shared" si="5"/>
         <v>15.013831492262245</v>
       </c>
+      <c r="L21" s="10">
+        <f t="shared" si="6"/>
+        <v>93.017271778256486</v>
+      </c>
     </row>
-    <row r="22" spans="1:11" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="22" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1898</v>
       </c>
       <c r="B22" s="4">
         <f t="shared" si="0"/>
         <v>1442210</v>
       </c>
-      <c r="C22" s="10">
+      <c r="C22" s="9">
         <f t="shared" si="1"/>
         <v>1452320</v>
       </c>
       <c r="D22" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1342210</v>
       </c>
       <c r="E22" s="4">
@@ -4288,15 +4363,15 @@
         <v>1352320</v>
       </c>
       <c r="F22" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>51700</v>
       </c>
       <c r="G22" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>31700</v>
       </c>
       <c r="H22" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>220</v>
       </c>
       <c r="I22" s="5">
@@ -4307,26 +4382,30 @@
         <f t="shared" si="4"/>
         <v>23.441197349739706</v>
       </c>
-      <c r="K22" s="11">
+      <c r="K22" s="10">
         <f t="shared" si="5"/>
         <v>14.789398958826315</v>
       </c>
+      <c r="L22" s="10">
+        <f t="shared" si="6"/>
+        <v>93.114465131651428</v>
+      </c>
     </row>
-    <row r="23" spans="1:11" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="23" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1899</v>
       </c>
       <c r="B23" s="4">
         <f t="shared" si="0"/>
         <v>1462430</v>
       </c>
-      <c r="C23" s="10">
+      <c r="C23" s="9">
         <f t="shared" si="1"/>
         <v>1472545</v>
       </c>
       <c r="D23" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1362430</v>
       </c>
       <c r="E23" s="4">
@@ -4334,15 +4413,15 @@
         <v>1372545</v>
       </c>
       <c r="F23" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>51800</v>
       </c>
       <c r="G23" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>31800</v>
       </c>
       <c r="H23" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>230</v>
       </c>
       <c r="I23" s="5">
@@ -4353,26 +4432,30 @@
         <f t="shared" si="4"/>
         <v>23.168639279586461</v>
       </c>
-      <c r="K23" s="11">
+      <c r="K23" s="10">
         <f t="shared" si="5"/>
         <v>14.571471245022931</v>
       </c>
+      <c r="L23" s="10">
+        <f t="shared" si="6"/>
+        <v>93.209036056623063</v>
+      </c>
     </row>
-    <row r="24" spans="1:11" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="24" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1900</v>
       </c>
       <c r="B24" s="4">
         <f t="shared" si="0"/>
         <v>1482660</v>
       </c>
-      <c r="C24" s="10">
+      <c r="C24" s="9">
         <f t="shared" si="1"/>
         <v>1492780</v>
       </c>
       <c r="D24" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1382660</v>
       </c>
       <c r="E24" s="4">
@@ -4380,15 +4463,15 @@
         <v>1392780</v>
       </c>
       <c r="F24" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>51900</v>
       </c>
       <c r="G24" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>31900</v>
       </c>
       <c r="H24" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>240</v>
       </c>
       <c r="I24" s="5">
@@ -4399,26 +4482,30 @@
         <f t="shared" si="4"/>
         <v>22.903832622524735</v>
       </c>
-      <c r="K24" s="11">
+      <c r="K24" s="10">
         <f t="shared" si="5"/>
         <v>14.359769669294504</v>
       </c>
+      <c r="L24" s="10">
+        <f t="shared" si="6"/>
+        <v>93.301089242889105</v>
+      </c>
     </row>
-    <row r="25" spans="1:11" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="25" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1901</v>
       </c>
       <c r="B25" s="4">
         <f t="shared" si="0"/>
         <v>1502900</v>
       </c>
-      <c r="C25" s="10">
+      <c r="C25" s="9">
         <f t="shared" si="1"/>
         <v>1513025</v>
       </c>
       <c r="D25" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1402900</v>
       </c>
       <c r="E25" s="4">
@@ -4426,15 +4513,15 @@
         <v>1413025</v>
       </c>
       <c r="F25" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>52000</v>
       </c>
       <c r="G25" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>32000</v>
       </c>
       <c r="H25" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>250</v>
       </c>
       <c r="I25" s="5">
@@ -4445,26 +4532,30 @@
         <f t="shared" si="4"/>
         <v>22.646449992038356</v>
       </c>
-      <c r="K25" s="11">
+      <c r="K25" s="10">
         <f t="shared" si="5"/>
         <v>14.154031245023972</v>
       </c>
+      <c r="L25" s="10">
+        <f t="shared" si="6"/>
+        <v>93.390723880966945</v>
+      </c>
     </row>
-    <row r="26" spans="1:11" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="26" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1902</v>
       </c>
       <c r="B26" s="4">
         <f t="shared" si="0"/>
         <v>1523150</v>
       </c>
-      <c r="C26" s="10">
+      <c r="C26" s="9">
         <f t="shared" si="1"/>
         <v>1533280</v>
       </c>
       <c r="D26" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1423150</v>
       </c>
       <c r="E26" s="4">
@@ -4472,15 +4563,15 @@
         <v>1433280</v>
       </c>
       <c r="F26" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>52100</v>
       </c>
       <c r="G26" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>32100</v>
       </c>
       <c r="H26" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>260</v>
       </c>
       <c r="I26" s="5">
@@ -4491,26 +4582,30 @@
         <f t="shared" si="4"/>
         <v>22.396182183523106</v>
       </c>
-      <c r="K26" s="11">
+      <c r="K26" s="10">
         <f t="shared" si="5"/>
         <v>13.95400759098013</v>
       </c>
+      <c r="L26" s="10">
+        <f t="shared" si="6"/>
+        <v>93.478034018574562</v>
+      </c>
     </row>
-    <row r="27" spans="1:11" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="27" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1903</v>
       </c>
       <c r="B27" s="4">
         <f t="shared" si="0"/>
         <v>1543410</v>
       </c>
-      <c r="C27" s="10">
+      <c r="C27" s="9">
         <f t="shared" si="1"/>
         <v>1553545</v>
       </c>
       <c r="D27" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1443410</v>
       </c>
       <c r="E27" s="4">
@@ -4518,15 +4613,15 @@
         <v>1453545</v>
       </c>
       <c r="F27" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>52200</v>
       </c>
       <c r="G27" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>32200</v>
       </c>
       <c r="H27" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>270</v>
       </c>
       <c r="I27" s="5">
@@ -4537,26 +4632,30 @@
         <f t="shared" si="4"/>
         <v>22.15273692936923</v>
       </c>
-      <c r="K27" s="11">
+      <c r="K27" s="10">
         <f t="shared" si="5"/>
         <v>13.759463931285243</v>
       </c>
+      <c r="L27" s="10">
+        <f t="shared" si="6"/>
+        <v>93.56310888966847</v>
+      </c>
     </row>
-    <row r="28" spans="1:11" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="28" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1904</v>
       </c>
       <c r="B28" s="4">
         <f t="shared" si="0"/>
         <v>1563680</v>
       </c>
-      <c r="C28" s="10">
+      <c r="C28" s="9">
         <f t="shared" si="1"/>
         <v>1573820</v>
       </c>
       <c r="D28" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1463680</v>
       </c>
       <c r="E28" s="4">
@@ -4564,15 +4663,15 @@
         <v>1473820</v>
       </c>
       <c r="F28" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>52300</v>
       </c>
       <c r="G28" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>32300</v>
       </c>
       <c r="H28" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>280</v>
       </c>
       <c r="I28" s="5">
@@ -4583,26 +4682,30 @@
         <f t="shared" si="4"/>
         <v>21.91583775494972</v>
       </c>
-      <c r="K28" s="11">
+      <c r="K28" s="10">
         <f t="shared" si="5"/>
         <v>13.570178176439455</v>
       </c>
+      <c r="L28" s="10">
+        <f t="shared" si="6"/>
+        <v>93.646033218538335</v>
+      </c>
     </row>
-    <row r="29" spans="1:11" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="29" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1905</v>
       </c>
       <c r="B29" s="4">
         <f t="shared" si="0"/>
         <v>1583960</v>
       </c>
-      <c r="C29" s="10">
+      <c r="C29" s="9">
         <f t="shared" si="1"/>
         <v>1594105</v>
       </c>
       <c r="D29" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1483960</v>
       </c>
       <c r="E29" s="4">
@@ -4610,15 +4713,15 @@
         <v>1494105</v>
       </c>
       <c r="F29" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>52400</v>
       </c>
       <c r="G29" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>32400</v>
       </c>
       <c r="H29" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>290</v>
       </c>
       <c r="I29" s="5">
@@ -4629,26 +4732,30 @@
         <f t="shared" si="4"/>
         <v>21.685222926099573</v>
       </c>
-      <c r="K29" s="11">
+      <c r="K29" s="10">
         <f t="shared" si="5"/>
         <v>13.385940077839233</v>
       </c>
+      <c r="L29" s="10">
+        <f t="shared" si="6"/>
+        <v>93.726887501137</v>
+      </c>
     </row>
-    <row r="30" spans="1:11" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="30" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1906</v>
       </c>
       <c r="B30" s="4">
         <f t="shared" si="0"/>
         <v>1604250</v>
       </c>
-      <c r="C30" s="10">
+      <c r="C30" s="9">
         <f t="shared" si="1"/>
         <v>1614400</v>
       </c>
       <c r="D30" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1504250</v>
       </c>
       <c r="E30" s="4">
@@ -4656,15 +4763,15 @@
         <v>1514400</v>
       </c>
       <c r="F30" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>52500</v>
       </c>
       <c r="G30" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>32500</v>
       </c>
       <c r="H30" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>300</v>
       </c>
       <c r="I30" s="5">
@@ -4675,26 +4782,30 @@
         <f t="shared" si="4"/>
         <v>21.460644479661912</v>
       </c>
-      <c r="K30" s="11">
+      <c r="K30" s="10">
         <f t="shared" si="5"/>
         <v>13.206550449022718</v>
       </c>
+      <c r="L30" s="10">
+        <f t="shared" si="6"/>
+        <v>93.805748265609509</v>
+      </c>
     </row>
-    <row r="31" spans="1:11" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="31" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1907</v>
       </c>
       <c r="B31" s="4">
         <f t="shared" si="0"/>
         <v>1624550</v>
       </c>
-      <c r="C31" s="10">
+      <c r="C31" s="9">
         <f t="shared" si="1"/>
         <v>1634705</v>
       </c>
       <c r="D31" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1524550</v>
       </c>
       <c r="E31" s="4">
@@ -4702,15 +4813,15 @@
         <v>1534705</v>
       </c>
       <c r="F31" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>52600</v>
       </c>
       <c r="G31" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>32600</v>
       </c>
       <c r="H31" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>310</v>
       </c>
       <c r="I31" s="5">
@@ -4721,26 +4832,30 @@
         <f t="shared" si="4"/>
         <v>21.241867329551933</v>
       </c>
-      <c r="K31" s="11">
+      <c r="K31" s="10">
         <f t="shared" si="5"/>
         <v>13.031820447577875</v>
       </c>
+      <c r="L31" s="10">
+        <f t="shared" si="6"/>
+        <v>93.882688313793622</v>
+      </c>
     </row>
-    <row r="32" spans="1:11" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="32" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1908</v>
       </c>
       <c r="B32" s="4">
         <f t="shared" si="0"/>
         <v>1644860</v>
       </c>
-      <c r="C32" s="10">
+      <c r="C32" s="9">
         <f t="shared" si="1"/>
         <v>1655020</v>
       </c>
       <c r="D32" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1544860</v>
       </c>
       <c r="E32" s="4">
@@ -4748,15 +4863,15 @@
         <v>1555020</v>
       </c>
       <c r="F32" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>52700</v>
       </c>
       <c r="G32" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>32700</v>
       </c>
       <c r="H32" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>320</v>
       </c>
       <c r="I32" s="5">
@@ -4767,26 +4882,30 @@
         <f t="shared" si="4"/>
         <v>21.028668441563454</v>
       </c>
-      <c r="K32" s="11">
+      <c r="K32" s="10">
         <f t="shared" si="5"/>
         <v>12.861570912271226</v>
       </c>
+      <c r="L32" s="10">
+        <f t="shared" si="6"/>
+        <v>93.957776945293716</v>
+      </c>
     </row>
-    <row r="33" spans="1:11" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="33" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1909</v>
       </c>
       <c r="B33" s="4">
         <f t="shared" si="0"/>
         <v>1665180</v>
       </c>
-      <c r="C33" s="10">
+      <c r="C33" s="9">
         <f t="shared" si="1"/>
         <v>1675345</v>
       </c>
       <c r="D33" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1565180</v>
       </c>
       <c r="E33" s="4">
@@ -4794,15 +4913,15 @@
         <v>1575345</v>
       </c>
       <c r="F33" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>52800</v>
       </c>
       <c r="G33" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>32800</v>
       </c>
       <c r="H33" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>330</v>
       </c>
       <c r="I33" s="5">
@@ -4813,26 +4932,30 @@
         <f t="shared" si="4"/>
         <v>20.820836070828928</v>
       </c>
-      <c r="K33" s="11">
+      <c r="K33" s="10">
         <f t="shared" si="5"/>
         <v>12.695631750505445</v>
       </c>
+      <c r="L33" s="10">
+        <f t="shared" si="6"/>
+        <v>94.031080165577833</v>
+      </c>
     </row>
-    <row r="34" spans="1:11" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="34" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1910</v>
       </c>
       <c r="B34" s="4">
         <f t="shared" si="0"/>
         <v>1685510</v>
       </c>
-      <c r="C34" s="10">
+      <c r="C34" s="9">
         <f t="shared" si="1"/>
         <v>1695680</v>
       </c>
       <c r="D34" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1585510</v>
       </c>
       <c r="E34" s="4">
@@ -4840,15 +4963,15 @@
         <v>1595680</v>
       </c>
       <c r="F34" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>52900</v>
       </c>
       <c r="G34" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>32900</v>
       </c>
       <c r="H34" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>340</v>
       </c>
       <c r="I34" s="5">
@@ -4859,26 +4982,30 @@
         <f t="shared" si="4"/>
         <v>20.61816905645242</v>
       </c>
-      <c r="K34" s="11">
+      <c r="K34" s="10">
         <f t="shared" si="5"/>
         <v>12.533841371703598</v>
       </c>
+      <c r="L34" s="10">
+        <f t="shared" si="6"/>
+        <v>94.102660879411218</v>
+      </c>
     </row>
-    <row r="35" spans="1:11" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="35" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1911</v>
       </c>
       <c r="B35" s="4">
         <f t="shared" si="0"/>
         <v>1705850</v>
       </c>
-      <c r="C35" s="10">
+      <c r="C35" s="9">
         <f t="shared" si="1"/>
         <v>1716025</v>
       </c>
       <c r="D35" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1605850</v>
       </c>
       <c r="E35" s="4">
@@ -4886,15 +5013,15 @@
         <v>1616025</v>
       </c>
       <c r="F35" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>53000</v>
       </c>
       <c r="G35" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>33000</v>
       </c>
       <c r="H35" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>350</v>
       </c>
       <c r="I35" s="5">
@@ -4905,26 +5032,30 @@
         <f t="shared" si="4"/>
         <v>20.420476168376108</v>
       </c>
-      <c r="K35" s="11">
+      <c r="K35" s="10">
         <f t="shared" si="5"/>
         <v>12.376046162652191</v>
       </c>
+      <c r="L35" s="10">
+        <f t="shared" si="6"/>
+        <v>94.172579070817733</v>
+      </c>
     </row>
-    <row r="36" spans="1:11" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="36" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1912</v>
       </c>
       <c r="B36" s="4">
         <f t="shared" si="0"/>
         <v>1726200</v>
       </c>
-      <c r="C36" s="10">
+      <c r="C36" s="9">
         <f t="shared" si="1"/>
         <v>1736380</v>
       </c>
       <c r="D36" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1626200</v>
       </c>
       <c r="E36" s="4">
@@ -4932,15 +5063,15 @@
         <v>1636380</v>
       </c>
       <c r="F36" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>53100</v>
       </c>
       <c r="G36" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>33100</v>
       </c>
       <c r="H36" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>360</v>
       </c>
       <c r="I36" s="5">
@@ -4951,26 +5082,30 @@
         <f t="shared" si="4"/>
         <v>20.227575502022759</v>
       </c>
-      <c r="K36" s="11">
+      <c r="K36" s="10">
         <f t="shared" si="5"/>
         <v>12.222100001222209</v>
       </c>
+      <c r="L36" s="10">
+        <f t="shared" si="6"/>
+        <v>94.240891970651589</v>
+      </c>
     </row>
-    <row r="37" spans="1:11" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="37" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1913</v>
       </c>
       <c r="B37" s="4">
         <f t="shared" si="0"/>
         <v>1746560</v>
       </c>
-      <c r="C37" s="10">
+      <c r="C37" s="9">
         <f t="shared" si="1"/>
         <v>1756745</v>
       </c>
       <c r="D37" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1646560</v>
       </c>
       <c r="E37" s="4">
@@ -4978,15 +5113,15 @@
         <v>1656745</v>
       </c>
       <c r="F37" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>53200</v>
       </c>
       <c r="G37" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>33200</v>
       </c>
       <c r="H37" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>370</v>
       </c>
       <c r="I37" s="5">
@@ -4997,12 +5132,16 @@
         <f t="shared" si="4"/>
         <v>20.039293916686031</v>
       </c>
-      <c r="K37" s="11">
+      <c r="K37" s="10">
         <f t="shared" si="5"/>
         <v>12.07186380523255</v>
       </c>
+      <c r="L37" s="10">
+        <f t="shared" si="6"/>
+        <v>94.307654212762799</v>
+      </c>
     </row>
-    <row r="38" spans="1:11" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="38" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <f>A37+1</f>
         <v>1914</v>
@@ -5011,9 +5150,9 @@
         <f t="shared" si="0"/>
         <v>1766930</v>
       </c>
-      <c r="C38" s="10"/>
+      <c r="C38" s="9"/>
       <c r="D38" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1666930</v>
       </c>
       <c r="E38" s="4"/>
@@ -5022,9 +5161,10 @@
       <c r="H38" s="4"/>
       <c r="I38" s="5"/>
       <c r="J38" s="5"/>
-      <c r="K38" s="11"/>
+      <c r="K38" s="10"/>
+      <c r="L38" s="10"/>
     </row>
-    <row r="39" spans="1:11" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="39" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" s="2"/>
       <c r="B39" s="4"/>
       <c r="C39" s="2"/>
@@ -5036,110 +5176,123 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="1"/>
+      <c r="L39" s="1"/>
     </row>
-    <row r="40" spans="1:11" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A40" s="13" t="s">
+    <row r="40" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A40" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="B40" s="13"/>
-      <c r="C40" s="13"/>
-      <c r="D40" s="13"/>
-      <c r="E40" s="13"/>
-      <c r="F40" s="14" cm="1">
+      <c r="B40" s="12"/>
+      <c r="C40" s="12"/>
+      <c r="D40" s="12"/>
+      <c r="E40" s="12"/>
+      <c r="F40" s="13" cm="1">
         <f t="array" ref="F40">SUM(F5+F5:F19)</f>
         <v>1510500</v>
       </c>
-      <c r="G40" s="14" cm="1">
+      <c r="G40" s="13" cm="1">
         <f t="array" ref="G40">SUM(G5+G5:G19)</f>
         <v>910500</v>
       </c>
-      <c r="H40" s="14" cm="1">
+      <c r="H40" s="13" cm="1">
         <f t="array" ref="H40">SUM(H5+H5:H19)</f>
         <v>2550</v>
       </c>
-      <c r="I40" s="12">
+      <c r="I40" s="11">
         <f>AVERAGE(I5:I19)</f>
         <v>44.284960471317206</v>
       </c>
-      <c r="J40" s="12">
+      <c r="J40" s="11">
         <f>AVERAGE(J5:J19)</f>
         <v>26.804245110008651</v>
       </c>
-      <c r="K40" s="12">
+      <c r="K40" s="11">
         <f>AVERAGE(K5:K19)</f>
         <v>17.480715361308548</v>
       </c>
+      <c r="L40" s="11">
+        <f>AVERAGE(L5:L19)</f>
+        <v>91.965609066958763</v>
+      </c>
     </row>
-    <row r="41" spans="1:11" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A41" s="13" t="s">
+    <row r="41" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A41" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="B41" s="13"/>
-      <c r="C41" s="13"/>
-      <c r="D41" s="13"/>
-      <c r="E41" s="13"/>
-      <c r="F41" s="14">
+      <c r="B41" s="12"/>
+      <c r="C41" s="12"/>
+      <c r="D41" s="12"/>
+      <c r="E41" s="12"/>
+      <c r="F41" s="13">
         <f>SUM(F20:F38)</f>
         <v>942300</v>
       </c>
-      <c r="G41" s="14">
+      <c r="G41" s="13">
         <f>SUM(G20:G38)</f>
         <v>582300</v>
       </c>
-      <c r="H41" s="14">
+      <c r="H41" s="13">
         <f>SUM(H20:H38)</f>
         <v>5130</v>
       </c>
-      <c r="I41" s="12">
+      <c r="I41" s="11">
         <f>AVERAGE(I20:I37)</f>
         <v>35.4279467724824</v>
       </c>
-      <c r="J41" s="12">
-        <f t="shared" ref="J41:K41" si="11">AVERAGE(J20:J37)</f>
+      <c r="J41" s="11">
+        <f t="shared" ref="J41:K41" si="12">AVERAGE(J20:J37)</f>
         <v>21.883358900395795</v>
       </c>
-      <c r="K41" s="12">
-        <f t="shared" si="11"/>
+      <c r="K41" s="11">
+        <f t="shared" si="12"/>
         <v>13.544587872086607</v>
       </c>
+      <c r="L41" s="11">
+        <f t="shared" ref="L41" si="13">AVERAGE(L20:L37)</f>
+        <v>93.659170831293736</v>
+      </c>
     </row>
-    <row r="42" spans="1:11" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A42" s="13" t="s">
+    <row r="42" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A42" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="B42" s="13"/>
-      <c r="C42" s="13"/>
-      <c r="D42" s="13"/>
-      <c r="E42" s="13"/>
-      <c r="F42" s="14">
+      <c r="B42" s="12"/>
+      <c r="C42" s="12"/>
+      <c r="D42" s="12"/>
+      <c r="E42" s="12"/>
+      <c r="F42" s="13">
         <f>F40+F41</f>
         <v>2452800</v>
       </c>
-      <c r="G42" s="14">
+      <c r="G42" s="13">
         <f>G40+G41</f>
         <v>1492800</v>
       </c>
-      <c r="H42" s="14">
+      <c r="H42" s="13">
         <f>H40+H41</f>
         <v>7680</v>
       </c>
-      <c r="I42" s="12">
+      <c r="I42" s="11">
         <f>AVERAGE(I5:I37)</f>
         <v>39.453862090134571</v>
       </c>
-      <c r="J42" s="12">
-        <f t="shared" ref="J42:K42" si="12">AVERAGE(J5:J37)</f>
+      <c r="J42" s="11">
+        <f t="shared" ref="J42:K42" si="14">AVERAGE(J5:J37)</f>
         <v>24.12012535931073</v>
       </c>
-      <c r="K42" s="12">
-        <f t="shared" si="12"/>
+      <c r="K42" s="11">
+        <f t="shared" si="14"/>
         <v>15.333736730823857</v>
+      </c>
+      <c r="L42" s="11">
+        <f t="shared" ref="L42" si="15">AVERAGE(L5:L37)</f>
+        <v>92.889370029323302</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="B3:C3"/>
-    <mergeCell ref="D3:J3"/>
+    <mergeCell ref="D3:L3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
